--- a/forms/반 명단 엑셀 (팀 이름으로 적기).xlsx
+++ b/forms/반 명단 엑셀 (팀 이름으로 적기).xlsx
@@ -5,7 +5,7 @@
   <x:workbookPr date1904="0" showBorderUnselectedTables="1" filterPrivacy="0" promptedSolutions="0" showInkAnnotation="1" backupFile="0" saveExternalLinkValues="1" codeName="ThisWorkbook" hidePivotFieldList="0" allowRefreshQuery="0" publishItems="0" checkCompatibility="0" autoCompressPictures="1" refreshAllConnections="0"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMSUNG\OneDrive\바탕 화면\수업도우미\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\SAMSUNG\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <x:bookViews>
@@ -19,99 +19,114 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="31">
+<x:sst xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="45" uniqueCount="36">
+  <x:si>
+    <x:t>수업월호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월요일２팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>몰입P2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화요일２팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수요일１팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수업요일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>세계사통사２호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수요일２팀</x:t>
+  </x:si>
   <x:si>
     <x:t>특이사항</x:t>
   </x:si>
   <x:si>
-    <x:t>수요일２팀</x:t>
-  </x:si>
-  <x:si>
     <x:t>화요일１팀</x:t>
   </x:si>
   <x:si>
     <x:t>과학탐탐</x:t>
   </x:si>
   <x:si>
-    <x:t>세계사통사２호</x:t>
-  </x:si>
-  <x:si>
     <x:t>월요일１팀</x:t>
   </x:si>
   <x:si>
-    <x:t>월요일２팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>몰입P2</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화요일２팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수요일１팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수업요일</x:t>
-  </x:si>
-  <x:si>
     <x:t>팀 여부</x:t>
   </x:si>
   <x:si>
+    <x:t>월요일 5:00~6:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수요일 4:00~6:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화요일 4:00~5:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>수요일 3:00~4:00</x:t>
+  </x:si>
+  <x:si>
+    <x:t>월요일 3:00~4:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>화요일 3:00~4:30</x:t>
+  </x:si>
+  <x:si>
+    <x:t>교과문학탐독１호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>논리１</x:t>
+  </x:si>
+  <x:si>
+    <x:t>개인</x:t>
+  </x:si>
+  <x:si>
     <x:t>인원</x:t>
   </x:si>
   <x:si>
-    <x:t>교과문학탐독１호</x:t>
+    <x:t>수업일</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">팀　</x:t>
+  </x:si>
+  <x:si>
+    <x:t>No</x:t>
+  </x:si>
+  <x:si>
+    <x:t>이름</x:t>
+  </x:si>
+  <x:si>
+    <x:t>단계</x:t>
+  </x:si>
+  <x:si>
+    <x:t>팀</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11월 2일, 9일, 16일, 23일</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11월 4일, 11일, 18일, 25일</x:t>
   </x:si>
   <x:si>
     <x:t>11월 3일, 10일, 17일 24일</x:t>
   </x:si>
   <x:si>
-    <x:t>11월 2일, 9일, 16일, 23일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>11월 4일, 11일, 18일, 25일</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화요일 4:00~5:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>화요일 3:00~4:30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수요일 3:00~4:00</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월요일 3:00~4:30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수요일 4:00~6:30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>월요일 5:00~6:30</x:t>
-  </x:si>
-  <x:si>
-    <x:t>개인</x:t>
-  </x:si>
-  <x:si>
-    <x:t>팀</x:t>
-  </x:si>
-  <x:si>
-    <x:t>논리１</x:t>
-  </x:si>
-  <x:si>
-    <x:t>이름</x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">팀　</x:t>
-  </x:si>
-  <x:si>
-    <x:t>No</x:t>
-  </x:si>
-  <x:si>
-    <x:t>단계</x:t>
-  </x:si>
-  <x:si>
-    <x:t>수업일</x:t>
+    <x:t>２호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>１호</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10월</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11월</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -587,7 +602,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <x:worksheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheetPr codeName="Sheet1"/>
-  <x:dimension ref="A1:H7"/>
+  <x:dimension ref="A1:I7"/>
   <x:sheetFormatPr defaultColWidth="9" defaultRowHeight="16.39999999999999857891"/>
   <x:cols>
     <x:col min="1" max="1" width="3.48046875" style="1" bestFit="1" customWidth="1"/>
@@ -595,167 +610,189 @@
     <x:col min="3" max="3" width="10.1875" style="1" bestFit="1" customWidth="1"/>
     <x:col min="4" max="4" width="22.59765625" style="1" bestFit="1" customWidth="1"/>
     <x:col min="5" max="5" width="15.69921875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="6" max="6" width="27.46875" style="1" bestFit="1" customWidth="1"/>
-    <x:col min="7" max="16384" width="9" style="1"/>
+    <x:col min="6" max="6" width="15.69921875" style="1" customWidth="1"/>
+    <x:col min="7" max="7" width="27.46875" style="1" bestFit="1" customWidth="1"/>
+    <x:col min="8" max="16384" width="9" style="1"/>
   </x:cols>
   <x:sheetData>
-    <x:row r="1" spans="1:8">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="4" t="s">
-        <x:v>28</x:v>
+        <x:v>25</x:v>
       </x:c>
       <x:c r="B1" s="4" t="s">
-        <x:v>11</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="C1" s="2" t="s">
         <x:v>26</x:v>
       </x:c>
       <x:c r="D1" s="2" t="s">
-        <x:v>10</x:v>
+        <x:v>5</x:v>
       </x:c>
       <x:c r="E1" s="2" t="s">
-        <x:v>29</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="F1" s="2" t="s">
-        <x:v>30</x:v>
+        <x:v>0</x:v>
       </x:c>
       <x:c r="G1" s="2" t="s">
-        <x:v>0</x:v>
-      </x:c>
-      <x:c r="H1" s="4" t="s">
-        <x:v>12</x:v>
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="H1" s="2" t="s">
+        <x:v>8</x:v>
+      </x:c>
+      <x:c r="I1" s="4" t="s">
+        <x:v>22</x:v>
       </x:c>
     </x:row>
-    <x:row r="2" spans="1:8">
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="5">
         <x:v>1</x:v>
       </x:c>
       <x:c r="B2" s="5" t="s">
-        <x:v>27</x:v>
+        <x:v>24</x:v>
       </x:c>
       <x:c r="C2" s="4" t="s">
-        <x:v>5</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="5" t="s">
-        <x:v>20</x:v>
+        <x:v>17</x:v>
       </x:c>
       <x:c r="E2" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F2" s="5" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G2" s="4"/>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G2" s="5" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="H2" s="4"/>
+      <x:c r="I2" s="4"/>
     </x:row>
-    <x:row r="3" spans="1:8">
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="4">
         <x:v>2</x:v>
       </x:c>
       <x:c r="B3" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C3" s="4" t="s">
-        <x:v>6</x:v>
+        <x:v>1</x:v>
       </x:c>
       <x:c r="D3" s="4" t="s">
-        <x:v>22</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="E3" s="4" t="s">
-        <x:v>7</x:v>
-      </x:c>
-      <x:c r="F3" s="3" t="s">
-        <x:v>15</x:v>
-      </x:c>
-      <x:c r="G3" s="4"/>
+        <x:v>2</x:v>
+      </x:c>
+      <x:c r="F3" s="4" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G3" s="3" t="s">
+        <x:v>29</x:v>
+      </x:c>
       <x:c r="H3" s="4"/>
+      <x:c r="I3" s="4"/>
     </x:row>
-    <x:row r="4" spans="1:8">
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="5">
         <x:v>3</x:v>
       </x:c>
       <x:c r="B4" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="4" t="s">
-        <x:v>2</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="D4" s="5" t="s">
         <x:v>18</x:v>
       </x:c>
       <x:c r="E4" s="5" t="s">
-        <x:v>3</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="F4" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G4" s="4"/>
+        <x:v>35</x:v>
+      </x:c>
+      <x:c r="G4" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="H4" s="4"/>
+      <x:c r="I4" s="4"/>
     </x:row>
-    <x:row r="5" spans="1:8">
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="5">
         <x:v>4</x:v>
       </x:c>
       <x:c r="B5" s="5" t="s">
-        <x:v>23</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="C5" s="4" t="s">
-        <x:v>8</x:v>
+        <x:v>3</x:v>
       </x:c>
       <x:c r="D5" s="5" t="s">
-        <x:v>17</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="E5" s="5" t="s">
-        <x:v>4</x:v>
-      </x:c>
-      <x:c r="F5" s="3" t="s">
-        <x:v>14</x:v>
-      </x:c>
-      <x:c r="G5" s="4"/>
+        <x:v>6</x:v>
+      </x:c>
+      <x:c r="F5" s="5" t="s">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G5" s="3" t="s">
+        <x:v>31</x:v>
+      </x:c>
       <x:c r="H5" s="4"/>
+      <x:c r="I5" s="4"/>
     </x:row>
-    <x:row r="6" spans="1:8">
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="4">
         <x:v>5</x:v>
       </x:c>
       <x:c r="B6" s="4" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C6" s="4" t="s">
-        <x:v>9</x:v>
+        <x:v>4</x:v>
       </x:c>
       <x:c r="D6" s="4" t="s">
-        <x:v>19</x:v>
+        <x:v>16</x:v>
       </x:c>
       <x:c r="E6" s="4" t="s">
-        <x:v>25</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="F6" s="4" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G6" s="4"/>
+        <x:v>34</x:v>
+      </x:c>
+      <x:c r="G6" s="4" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="H6" s="4"/>
+      <x:c r="I6" s="4"/>
     </x:row>
-    <x:row r="7" spans="1:8">
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="5">
         <x:v>6</x:v>
       </x:c>
       <x:c r="B7" s="5" t="s">
-        <x:v>24</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C7" s="4" t="s">
-        <x:v>1</x:v>
+        <x:v>7</x:v>
       </x:c>
       <x:c r="D7" s="5" t="s">
-        <x:v>21</x:v>
+        <x:v>14</x:v>
       </x:c>
       <x:c r="E7" s="5" t="s">
-        <x:v>13</x:v>
-      </x:c>
-      <x:c r="F7" s="3" t="s">
-        <x:v>16</x:v>
-      </x:c>
-      <x:c r="G7" s="4"/>
+        <x:v>19</x:v>
+      </x:c>
+      <x:c r="F7" s="5" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="G7" s="3" t="s">
+        <x:v>30</x:v>
+      </x:c>
       <x:c r="H7" s="4"/>
+      <x:c r="I7" s="4"/>
     </x:row>
   </x:sheetData>
   <x:pageMargins left="0.74805557727813720703" right="0.74805557727813720703" top="0.98430556058883666992" bottom="0.98430556058883666992" header="0.51138889789581298828" footer="0.51138889789581298828"/>
